--- a/output/pdf_financials_xlsx/ELC.xlsx
+++ b/output/pdf_financials_xlsx/ELC.xlsx
@@ -6448,7 +6448,7 @@
         <v>13.190903</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>13.231208</v>
+        <v>13.362272</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>13.578342</v>
@@ -8015,19 +8015,19 @@
         <v>0</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.01572</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.014355</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.01724</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.07679900000000001</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.0002</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
@@ -15492,7 +15492,11 @@
           <t>Warrant reserve 12</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -27878,7 +27882,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -29758,7 +29766,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -32370,7 +32382,11 @@
           <t>Exploration and evaluation expenditures 7</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -34266,7 +34282,11 @@
           <t>Purchase of exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -34370,7 +34390,11 @@
           <t>Recovery of exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ELC.xlsx
+++ b/output/pdf_financials_xlsx/ELC.xlsx
@@ -1135,30 +1135,28 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.27956</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.767768</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.166287</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.034269</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.063373</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.070621</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.08057599999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.073518</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0.06904399999999999</v>
@@ -2190,13 +2188,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.91625</v>
+        <v>-9.19581</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.489209</v>
+        <v>-7.256977</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-6.489209</v>
+        <v>-6.655496</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2204,16 +2202,16 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.726357</v>
+        <v>-1.78973</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.475613</v>
+        <v>-3.546234</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.673069</v>
+        <v>0.592493</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.804549</v>
+        <v>1.731031</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>0.675235</v>
@@ -2322,13 +2320,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.91625</v>
+        <v>-9.19581</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.489209</v>
+        <v>-7.256977</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-6.489209</v>
+        <v>-6.655496</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2336,16 +2334,16 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.71032</v>
+        <v>-1.773693</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.465973</v>
+        <v>-3.536594</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.678862</v>
+        <v>0.598286</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.805627</v>
+        <v>1.732109</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0.675726</v>
@@ -2698,7 +2696,7 @@
         <v>1.532977</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>5.115658</v>
       </c>
     </row>
     <row r="35">
@@ -2824,7 +2822,7 @@
         <v>11.572878</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>16.205505</v>
+        <v>21.321163</v>
       </c>
     </row>
     <row r="37">
@@ -3580,7 +3578,7 @@
         <v>0.227832</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>5.329594</v>
+        <v>0.213936</v>
       </c>
     </row>
     <row r="49">
@@ -9308,7 +9306,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -58518,7 +58516,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -59262,7 +59260,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -64722,7 +64720,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -67026,7 +67024,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E555" s="5" t="n">

--- a/output/pdf_financials_xlsx/ELC.xlsx
+++ b/output/pdf_financials_xlsx/ELC.xlsx
@@ -827,37 +827,37 @@
         <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.228752</v>
+        <v>0.264752</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.255567</v>
+        <v>0.282067</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.336834</v>
+        <v>0.363834</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.31719</v>
+        <v>0.339365</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.316172</v>
+        <v>0.338722</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.344788</v>
+        <v>0.367338</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.328142</v>
+        <v>0.340942</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.324915</v>
+        <v>0.337215</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.236618</v>
+        <v>0.254104</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.247492</v>
+        <v>0.266707</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.4561</v>
+        <v>0.475315</v>
       </c>
     </row>
     <row r="8">
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.239506</v>
+        <v>0.275506</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.018943</v>
@@ -1028,25 +1028,25 @@
         <v>0.032919</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.322528</v>
+        <v>0.345078</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.362842</v>
+        <v>0.385392</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.336848</v>
+        <v>0.349648</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.376835</v>
+        <v>0.389135</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.289633</v>
+        <v>0.307119</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.294477</v>
+        <v>0.313692</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.50627</v>
+        <v>0.525485</v>
       </c>
     </row>
     <row r="11">
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.208926</v>
+        <v>0.196126</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-1.949983</v>
+        <v>-1.962283</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-3.786635</v>
+        <v>-3.804121</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.9661650000000001</v>
+        <v>0.94695</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>10.841778</v>
+        <v>10.822563</v>
       </c>
     </row>
     <row r="12">
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-7.91625</v>
+        <v>-0.792612</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-6.489209</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-6.489209</v>
+        <v>-6.384619</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -1456,13 +1456,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-7.123638</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.10459</v>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-1.726357</v>
+        <v>-1.665646</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-3.475613</v>
+        <v>-1.274999</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.673069</v>
+        <v>-0.309219</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.804549</v>
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-9.19581</v>
+        <v>-2.072172</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-7.256977</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-6.655496</v>
+        <v>-6.550906</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-9.19581</v>
+        <v>-2.072172</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-7.256977</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-6.655496</v>
+        <v>-6.550906</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-898.7547501173335</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.638155698875689</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -4775,49 +4775,49 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>1.486965</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>1.471132</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>1.468132</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>1.090217</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.026207</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.017258</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.027309</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.032563</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.03049</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="68">
@@ -4841,46 +4841,46 @@
         <v>1.71364</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1.643829</v>
+        <v>3.114961</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1.469037</v>
+        <v>2.937169</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>1.11553</v>
+        <v>2.205747</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.034174</v>
+        <v>0.060381</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.024187</v>
+        <v>0.041445</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.028929</v>
+        <v>0.056238</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.033811</v>
+        <v>0.066374</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.049805</v>
+        <v>0.079805</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.031984</v>
+        <v>0.062474</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.048313</v>
+        <v>0.09331299999999999</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.065804</v>
+        <v>0.115804</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.062087</v>
+        <v>0.117087</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>0.068192</v>
+        <v>0.128192</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>0.067672</v>
+        <v>0.127672</v>
       </c>
     </row>
     <row r="69">
@@ -5321,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>0.175</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="76">
@@ -7522,7 +7522,7 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.00755</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -7561,10 +7561,10 @@
         <v>0</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.024759</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>0.046851</v>
       </c>
     </row>
     <row r="111">
@@ -7778,13 +7778,13 @@
         <v>0</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-2.704813</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0</v>
+        <v>-2.278377</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0</v>
+        <v>-10.254016</v>
       </c>
       <c r="L114" s="3" t="n">
         <v>-4.912203</v>
@@ -7839,37 +7839,37 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.329646</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>2.739365</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>7.740495</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>5.917009</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>9.499561</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>6.870043</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>9.381727</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>4.592566</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>3.488</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>3.621519</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>13.928261</v>
       </c>
     </row>
     <row r="116">
@@ -18038,7 +18038,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -18980,7 +18984,11 @@
           <t>Proceeds from sale of investments 6</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -21458,7 +21466,11 @@
           <t>Proceeds from sale of investments 6</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -23294,7 +23306,11 @@
           <t>Proceeds from sale of investments 6</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -25868,7 +25884,11 @@
           <t>Proceeds from sale of investments 7</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -26718,7 +26738,11 @@
           <t>Purchase of marketable securities 7</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -26822,7 +26846,11 @@
           <t>Proceeds from sale of marketable securities 7</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -28094,7 +28122,11 @@
           <t>Purchase of marketable securities 7</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -28196,7 +28228,11 @@
           <t>Proceeds from sale of marketable securities 7</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -35668,7 +35704,11 @@
           <t>Accretion 7,550</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -48714,7 +48754,11 @@
           <t>Director fees 14</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -52206,7 +52250,11 @@
           <t>Director fees 13</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -56602,7 +56650,11 @@
           <t>Director fees 15</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E456" t="inlineStr">
         <is>
           <t>-</t>
@@ -57558,7 +57610,11 @@
           <t>Director fees 17</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr">
         <is>
           <t>-</t>
@@ -61566,7 +61622,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
           <t>-</t>
@@ -65462,7 +65522,11 @@
           <t>Future income tax recovery (Note 13) 9,833,756</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
@@ -67550,7 +67614,11 @@
           <t>Future income tax recovery (Note 14) 9,833,756</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr"/>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E560" s="5" t="n">
         <v>7.123638</v>
       </c>
